--- a/JellyFin_Server.xlsx
+++ b/JellyFin_Server.xlsx
@@ -4,7 +4,7 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="7" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="Movies SELECTED" sheetId="1" state="visible" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="2970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="2971">
   <si>
     <t>Title</t>
   </si>
@@ -8945,6 +8945,9 @@
   </si>
   <si>
     <t xml:space="preserve">Carioquismo Cultural</t>
+  </si>
+  <si>
+    <t>Gladiodrome</t>
   </si>
 </sst>
 </file>
@@ -9070,7 +9073,7 @@
       <protection hidden="0" locked="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -9176,6 +9179,9 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -29526,6 +29532,9 @@
       <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="8" t="s">
@@ -32392,6 +32401,14 @@
         <v>2944</v>
       </c>
     </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="29" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>2253</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="previous" ref="F5"/>
